--- a/hdw/weather-station-v1/weather-station-v1-bom.xlsx
+++ b/hdw/weather-station-v1/weather-station-v1-bom.xlsx
@@ -3,26 +3,23 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A12A39-CA49-4AD6-B86F-1EF3C0AB5401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64637A0E-F1FB-44A6-B193-A17B4FB68C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="240" windowWidth="29040" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_weather-station-v1_main-sch" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="60">
   <si>
     <t>Quantity</t>
   </si>
   <si>
-    <t>Designator</t>
-  </si>
-  <si>
     <t>Value</t>
   </si>
   <si>
@@ -71,9 +68,6 @@
     <t>330k</t>
   </si>
   <si>
-    <t>R2,R3</t>
-  </si>
-  <si>
     <t>100k</t>
   </si>
   <si>
@@ -89,15 +83,6 @@
     <t>470</t>
   </si>
   <si>
-    <t>R9,R10</t>
-  </si>
-  <si>
-    <t>LED1,LED2,LED3</t>
-  </si>
-  <si>
-    <t>Q1,Q2,Q3</t>
-  </si>
-  <si>
     <t>SW1</t>
   </si>
   <si>
@@ -119,18 +104,12 @@
     <t>U5</t>
   </si>
   <si>
-    <t>CONN,REG,BLD_IN</t>
-  </si>
-  <si>
     <t>BME280</t>
   </si>
   <si>
     <t>buck-boost DC-DC</t>
   </si>
   <si>
-    <t>TODO</t>
-  </si>
-  <si>
     <t>TP4056 CHARGING MODDULE</t>
   </si>
   <si>
@@ -146,23 +125,83 @@
     <t>6x6 mm tact switch</t>
   </si>
   <si>
-    <t>5mm THT LEDs</t>
-  </si>
-  <si>
     <t>ESP8266 THT adapter board</t>
   </si>
   <si>
-    <t>universal PCB prototype board</t>
-  </si>
-  <si>
     <t>female goldpins</t>
+  </si>
+  <si>
+    <t>Designators</t>
+  </si>
+  <si>
+    <t>Universal PCB prototype board</t>
+  </si>
+  <si>
+    <t>R2,R3,R9,R10</t>
+  </si>
+  <si>
+    <t>TME</t>
+  </si>
+  <si>
+    <t>Botland</t>
+  </si>
+  <si>
+    <t>Store</t>
+  </si>
+  <si>
+    <t>Price per Unit</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>LED2</t>
+  </si>
+  <si>
+    <t>LED3</t>
+  </si>
+  <si>
+    <t>LED1</t>
+  </si>
+  <si>
+    <t>BLD_IN</t>
+  </si>
+  <si>
+    <t>REG</t>
+  </si>
+  <si>
+    <t>CONN</t>
+  </si>
+  <si>
+    <t>5mm red LED</t>
+  </si>
+  <si>
+    <t>5mm green LED</t>
+  </si>
+  <si>
+    <t>blue LED build into ESP8266</t>
+  </si>
+  <si>
+    <t>18650 BATTERY</t>
+  </si>
+  <si>
+    <t>`</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>Q2,Q3</t>
+  </si>
+  <si>
+    <t>Q1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -172,6 +211,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -194,13 +241,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperłącze" xfId="1" builtinId="8"/>
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -538,331 +588,697 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="26.140625" customWidth="1"/>
+    <col min="2" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="29.7109375" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" customWidth="1"/>
+    <col min="9" max="9" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
       </c>
       <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2">
+        <v>0.87</v>
+      </c>
+      <c r="I2">
+        <f>H2*F2</f>
+        <v>2.61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3">
+        <v>0.87</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I26" si="0">H3*F3</f>
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>2.2400000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6">
+        <v>1.18</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7">
+        <v>0.38</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8">
+        <v>1.38</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9">
+        <v>1.08</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="B10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11">
+        <v>3.34</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="G12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12">
+        <v>6.88</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>13.76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="0"/>
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H15">
+        <v>3.9</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="0"/>
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="D6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16">
+        <v>29.9</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="0"/>
+        <v>29.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17">
+        <v>34.9</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="0"/>
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="0"/>
+        <v>17.899999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>0.1</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+      <c r="H20">
+        <v>0.1</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21">
         <v>2</v>
       </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="H21">
+        <v>0.1</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22">
+        <v>3</v>
+      </c>
+      <c r="H22">
+        <v>0.1</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="0"/>
+        <v>0.30000000000000004</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="E23" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H23">
+        <v>2.9</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="0"/>
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="E24" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="H24">
+        <v>5.9</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="0"/>
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="E25" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>2</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="D8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>1</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>1</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>1</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>1</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>1</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>1</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>2</v>
-      </c>
-      <c r="B17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>2</v>
-      </c>
-      <c r="B18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>3</v>
-      </c>
-      <c r="B19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>2</v>
-      </c>
-      <c r="B20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>1</v>
-      </c>
-      <c r="E21" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>1</v>
-      </c>
-      <c r="E22" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>1</v>
-      </c>
-      <c r="E23" t="s">
-        <v>46</v>
+      <c r="E26" t="s">
+        <v>55</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H26">
+        <v>29.9</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="0"/>
+        <v>29.9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I27">
+        <f>SUM(I2:I26)</f>
+        <v>163.57000000000002</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{73B3DE33-9A59-4692-9E2E-6EE2E03B61D7}"/>
+    <hyperlink ref="G4" r:id="rId2" xr:uid="{08F8E6A5-C646-41B7-A9BF-AF0CFA1E03B5}"/>
+    <hyperlink ref="G3" r:id="rId3" xr:uid="{CC77DB99-EDD9-4D58-93FC-5E198D6D7C89}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{AAEF6E25-5B4B-4C76-9267-D8B787D3CD91}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{68A6D9A1-5260-4CB0-B1F4-A10B6D9E5045}"/>
+    <hyperlink ref="G7" r:id="rId6" xr:uid="{9861BFDD-5CEC-42BB-8FD0-2E90E21D601E}"/>
+    <hyperlink ref="G8" r:id="rId7" xr:uid="{526BEBEE-D55F-4FB8-941D-BA2E55D188C2}"/>
+    <hyperlink ref="G9" r:id="rId8" xr:uid="{B9642C7F-E5EC-4534-80F0-7B42FC50AFDE}"/>
+    <hyperlink ref="G24" r:id="rId9" xr:uid="{3621D474-1ED7-4957-A90C-6EAA38344D65}"/>
+    <hyperlink ref="G18" r:id="rId10" xr:uid="{D5AB0335-18D0-4A0E-BE84-6E91B82417E7}"/>
+    <hyperlink ref="G23" r:id="rId11" xr:uid="{924692B1-C10F-4DD7-86B6-FC39008B2ACA}"/>
+    <hyperlink ref="G14" r:id="rId12" xr:uid="{2EC3CCD9-0996-44F0-9336-DD16EABB1BC5}"/>
+    <hyperlink ref="G17" r:id="rId13" xr:uid="{A97E0E0D-4FF4-48F7-9F97-578C2A03AB80}"/>
+    <hyperlink ref="G15" r:id="rId14" xr:uid="{05ED4C53-3A72-47FA-B604-E8051A03B8C3}"/>
+    <hyperlink ref="G26" r:id="rId15" xr:uid="{C544BB5E-44BA-4411-9A34-D3113DFAA6D6}"/>
+    <hyperlink ref="G16" r:id="rId16" xr:uid="{C7D3988A-3FF7-4EF4-AEF9-EB52B1CB7B84}"/>
+    <hyperlink ref="G12" r:id="rId17" xr:uid="{D1DCAE8E-8BA0-4269-801A-C5F5AC88ACBD}"/>
+    <hyperlink ref="G11" r:id="rId18" xr:uid="{9064F519-8F9C-4ECF-961B-D7376CF3A626}"/>
+  </hyperlinks>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
